--- a/pca-interpretable-clustering/classified_data/Nitride.xlsx
+++ b/pca-interpretable-clustering/classified_data/Nitride.xlsx
@@ -3558,7 +3558,7 @@
         <v>151.59901</v>
       </c>
       <c r="H2">
-        <v>616.12289</v>
+        <v>616.122895</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -3584,7 +3584,7 @@
         <v>109.33265</v>
       </c>
       <c r="H3">
-        <v>406.07713</v>
+        <v>406.0771306</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -3610,7 +3610,7 @@
         <v>115.82228</v>
       </c>
       <c r="H4">
-        <v>506.19795</v>
+        <v>506.1979531</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3636,7 +3636,7 @@
         <v>106.84009</v>
       </c>
       <c r="H5">
-        <v>455.62304</v>
+        <v>455.6230415</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -3662,7 +3662,7 @@
         <v>135.55921</v>
       </c>
       <c r="H6">
-        <v>479.04396</v>
+        <v>479.0439607</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -3688,7 +3688,7 @@
         <v>87.5004</v>
       </c>
       <c r="H7">
-        <v>343.42912</v>
+        <v>343.429117</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -3714,7 +3714,7 @@
         <v>75.37130999999999</v>
       </c>
       <c r="H8">
-        <v>306.52299</v>
+        <v>306.5229918</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -3740,7 +3740,7 @@
         <v>5.36012</v>
       </c>
       <c r="H9">
-        <v>84.75402</v>
+        <v>84.75402192999999</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -3766,7 +3766,7 @@
         <v>26.88224</v>
       </c>
       <c r="H10">
-        <v>350.14256</v>
+        <v>350.1425574</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -3792,7 +3792,7 @@
         <v>76.13683</v>
       </c>
       <c r="H11">
-        <v>302.15329</v>
+        <v>302.1532914</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -3818,7 +3818,7 @@
         <v>121.80507</v>
       </c>
       <c r="H12">
-        <v>460.55418</v>
+        <v>460.5541776</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -3844,7 +3844,7 @@
         <v>48.00498</v>
       </c>
       <c r="H13">
-        <v>478.05018</v>
+        <v>478.0501805</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -3870,7 +3870,7 @@
         <v>9.99728</v>
       </c>
       <c r="H14">
-        <v>191.51876</v>
+        <v>191.518758</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -3896,7 +3896,7 @@
         <v>63.39666</v>
       </c>
       <c r="H15">
-        <v>304.77456</v>
+        <v>304.7745618</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -3922,7 +3922,7 @@
         <v>95.48473</v>
       </c>
       <c r="H16">
-        <v>321.28835</v>
+        <v>321.2883465</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -3948,7 +3948,7 @@
         <v>124.1909</v>
       </c>
       <c r="H17">
-        <v>540.97066</v>
+        <v>540.9706596</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -3974,7 +3974,7 @@
         <v>111.35907</v>
       </c>
       <c r="H18">
-        <v>524.50731</v>
+        <v>524.5073132</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -4000,7 +4000,7 @@
         <v>158.16512</v>
       </c>
       <c r="H19">
-        <v>933.28966</v>
+        <v>933.2896596</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -4026,7 +4026,7 @@
         <v>52.72299</v>
       </c>
       <c r="H20">
-        <v>271.38521</v>
+        <v>271.3852134</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -4052,7 +4052,7 @@
         <v>285.88392</v>
       </c>
       <c r="H21">
-        <v>631.67421</v>
+        <v>550.3017324</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -4078,7 +4078,7 @@
         <v>92.50020000000001</v>
       </c>
       <c r="H22">
-        <v>395.26705</v>
+        <v>395.267055</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -4104,7 +4104,7 @@
         <v>334.96286</v>
       </c>
       <c r="H23">
-        <v>521.40698</v>
+        <v>537.7089737</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -4130,7 +4130,7 @@
         <v>82.1408</v>
       </c>
       <c r="H24">
-        <v>343.69141</v>
+        <v>343.6914057</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -4156,7 +4156,7 @@
         <v>128.17272</v>
       </c>
       <c r="H25">
-        <v>529.55081</v>
+        <v>529.5508104</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -4182,7 +4182,7 @@
         <v>98.75691</v>
       </c>
       <c r="H26">
-        <v>361.63401</v>
+        <v>361.6340108</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -4208,7 +4208,7 @@
         <v>98.2513</v>
       </c>
       <c r="H27">
-        <v>318.89513</v>
+        <v>318.8951327</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -4234,7 +4234,7 @@
         <v>100.08019</v>
       </c>
       <c r="H28">
-        <v>385.25368</v>
+        <v>385.2536835</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -4260,7 +4260,7 @@
         <v>31.63446</v>
       </c>
       <c r="H29">
-        <v>271.25639</v>
+        <v>271.2563936</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -4286,7 +4286,7 @@
         <v>247.72594</v>
       </c>
       <c r="H30">
-        <v>661.3862800000001</v>
+        <v>661.3862773</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -4312,7 +4312,7 @@
         <v>96.54541999999999</v>
       </c>
       <c r="H31">
-        <v>366.04562</v>
+        <v>436.1363504</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -4338,7 +4338,7 @@
         <v>347.24071</v>
       </c>
       <c r="H32">
-        <v>852.31544</v>
+        <v>852.3154361000001</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -4364,7 +4364,7 @@
         <v>413.71387</v>
       </c>
       <c r="H33">
-        <v>1189.60914</v>
+        <v>1189.609137</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -4390,7 +4390,7 @@
         <v>116.68664</v>
       </c>
       <c r="H34">
-        <v>567.26482</v>
+        <v>567.2648218</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -4416,7 +4416,7 @@
         <v>213.16457</v>
       </c>
       <c r="H35">
-        <v>640.6564</v>
+        <v>640.656404</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -4442,7 +4442,7 @@
         <v>262.41446</v>
       </c>
       <c r="H36">
-        <v>872.58775</v>
+        <v>872.5877521</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -4468,7 +4468,7 @@
         <v>157.21457</v>
       </c>
       <c r="H37">
-        <v>480.71524</v>
+        <v>480.7152359</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -4494,7 +4494,7 @@
         <v>149.04141</v>
       </c>
       <c r="H38">
-        <v>494.6729</v>
+        <v>494.6728976</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -4520,7 +4520,7 @@
         <v>239.34847</v>
       </c>
       <c r="H39">
-        <v>586.5262300000001</v>
+        <v>586.5262312999999</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -4546,7 +4546,7 @@
         <v>167.58168</v>
       </c>
       <c r="H40">
-        <v>442.74812</v>
+        <v>391.2600605</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -4572,7 +4572,7 @@
         <v>146.98804</v>
       </c>
       <c r="H41">
-        <v>746.8704</v>
+        <v>746.8703956000001</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -4598,7 +4598,7 @@
         <v>197.66325</v>
       </c>
       <c r="H42">
-        <v>571.68807</v>
+        <v>570.6812093</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -4624,7 +4624,7 @@
         <v>210.37968</v>
       </c>
       <c r="H43">
-        <v>626.84783</v>
+        <v>626.8478303000001</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -4650,7 +4650,7 @@
         <v>290.06558</v>
       </c>
       <c r="H44">
-        <v>983.69829</v>
+        <v>983.6982923</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -4676,7 +4676,7 @@
         <v>122.88709</v>
       </c>
       <c r="H45">
-        <v>406.06831</v>
+        <v>406.0683053</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -4702,7 +4702,7 @@
         <v>136.11985</v>
       </c>
       <c r="H46">
-        <v>577.66728</v>
+        <v>577.667277</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -4728,7 +4728,7 @@
         <v>219.84337</v>
       </c>
       <c r="H47">
-        <v>796.15723</v>
+        <v>796.1572303</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -4754,7 +4754,7 @@
         <v>151.07858</v>
       </c>
       <c r="H48">
-        <v>515.31898</v>
+        <v>515.3189836</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -4780,7 +4780,7 @@
         <v>140.44523</v>
       </c>
       <c r="H49">
-        <v>433.99718</v>
+        <v>433.9971798</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -4806,7 +4806,7 @@
         <v>142.38857</v>
       </c>
       <c r="H50">
-        <v>595.03824</v>
+        <v>595.038238</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -4832,7 +4832,7 @@
         <v>196.08194</v>
       </c>
       <c r="H51">
-        <v>583.76653</v>
+        <v>583.7665311</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -4858,7 +4858,7 @@
         <v>288.46692</v>
       </c>
       <c r="H52">
-        <v>913.46955</v>
+        <v>913.4695524</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -4884,7 +4884,7 @@
         <v>140.23562</v>
       </c>
       <c r="H53">
-        <v>433.29073</v>
+        <v>433.2907333</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -4910,7 +4910,7 @@
         <v>206.91684</v>
       </c>
       <c r="H54">
-        <v>538.68713</v>
+        <v>590.7987033000001</v>
       </c>
     </row>
     <row r="55" spans="1:8">
@@ -4936,7 +4936,7 @@
         <v>160.2826</v>
       </c>
       <c r="H55">
-        <v>497.90791</v>
+        <v>497.9079083</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -4962,7 +4962,7 @@
         <v>258.93136</v>
       </c>
       <c r="H56">
-        <v>755.819</v>
+        <v>777.7152688</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -4988,7 +4988,7 @@
         <v>244.94499</v>
       </c>
       <c r="H57">
-        <v>780.5842</v>
+        <v>780.5841974</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -5014,7 +5014,7 @@
         <v>115.89068</v>
       </c>
       <c r="H58">
-        <v>427.94963</v>
+        <v>461.3373075</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -5040,7 +5040,7 @@
         <v>45.228</v>
       </c>
       <c r="H59">
-        <v>196.44591</v>
+        <v>196.4459147</v>
       </c>
     </row>
     <row r="60" spans="1:8">
@@ -5066,7 +5066,7 @@
         <v>98.70242</v>
       </c>
       <c r="H60">
-        <v>451.99887</v>
+        <v>451.9988685</v>
       </c>
     </row>
     <row r="61" spans="1:8">
@@ -5092,7 +5092,7 @@
         <v>114.28937</v>
       </c>
       <c r="H61">
-        <v>494.26704</v>
+        <v>494.2670395</v>
       </c>
     </row>
     <row r="62" spans="1:8">
@@ -5118,7 +5118,7 @@
         <v>37.9756</v>
       </c>
       <c r="H62">
-        <v>258.54311</v>
+        <v>258.5431113</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -5144,7 +5144,7 @@
         <v>47.72185</v>
       </c>
       <c r="H63">
-        <v>273.09567</v>
+        <v>273.0956735</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -5170,7 +5170,7 @@
         <v>41.37312</v>
       </c>
       <c r="H64">
-        <v>224.29701</v>
+        <v>224.2970128</v>
       </c>
     </row>
     <row r="65" spans="1:8">
@@ -5196,7 +5196,7 @@
         <v>51.96454</v>
       </c>
       <c r="H65">
-        <v>337.8498</v>
+        <v>337.8498044</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -5222,7 +5222,7 @@
         <v>36.26337</v>
       </c>
       <c r="H66">
-        <v>196.12774</v>
+        <v>196.1277396</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -5248,7 +5248,7 @@
         <v>187.80763</v>
       </c>
       <c r="H67">
-        <v>684.87086</v>
+        <v>684.8708571</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -5274,7 +5274,7 @@
         <v>132.67142</v>
       </c>
       <c r="H68">
-        <v>562.13202</v>
+        <v>562.1320176</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -5300,7 +5300,7 @@
         <v>254.44282</v>
       </c>
       <c r="H69">
-        <v>583.49643</v>
+        <v>583.4964293</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -5326,7 +5326,7 @@
         <v>108.81209</v>
       </c>
       <c r="H70">
-        <v>444.07741</v>
+        <v>444.0774128</v>
       </c>
     </row>
     <row r="71" spans="1:8">
@@ -5352,7 +5352,7 @@
         <v>21.73528</v>
       </c>
       <c r="H71">
-        <v>265.97373</v>
+        <v>265.9737251</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -5378,7 +5378,7 @@
         <v>79.20834000000001</v>
       </c>
       <c r="H72">
-        <v>391.21703</v>
+        <v>391.2170255</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -5404,7 +5404,7 @@
         <v>102.37537</v>
       </c>
       <c r="H73">
-        <v>567.22005</v>
+        <v>567.2200483</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -5430,7 +5430,7 @@
         <v>150.3371</v>
       </c>
       <c r="H74">
-        <v>529.97195</v>
+        <v>529.9719527</v>
       </c>
     </row>
     <row r="75" spans="1:8">
@@ -5456,7 +5456,7 @@
         <v>147.11933</v>
       </c>
       <c r="H75">
-        <v>460.50832</v>
+        <v>460.5083161</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -5482,7 +5482,7 @@
         <v>75.1944</v>
       </c>
       <c r="H76">
-        <v>385.91664</v>
+        <v>385.9166422</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -5508,7 +5508,7 @@
         <v>48.29769</v>
       </c>
       <c r="H77">
-        <v>253.44419</v>
+        <v>253.4441862</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -5534,7 +5534,7 @@
         <v>88.14519</v>
       </c>
       <c r="H78">
-        <v>329.89313</v>
+        <v>329.8931274</v>
       </c>
     </row>
     <row r="79" spans="1:8">
@@ -5560,7 +5560,7 @@
         <v>22.0514</v>
       </c>
       <c r="H79">
-        <v>162.71664</v>
+        <v>162.7166402</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -5586,7 +5586,7 @@
         <v>70.32472</v>
       </c>
       <c r="H80">
-        <v>259.33737</v>
+        <v>259.3373656</v>
       </c>
     </row>
     <row r="81" spans="1:8">
@@ -5612,7 +5612,7 @@
         <v>73.59422000000001</v>
       </c>
       <c r="H81">
-        <v>325.93003</v>
+        <v>325.9300263</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -5638,7 +5638,7 @@
         <v>129.39264</v>
       </c>
       <c r="H82">
-        <v>527.94454</v>
+        <v>527.9445423</v>
       </c>
     </row>
     <row r="83" spans="1:8">
@@ -5664,7 +5664,7 @@
         <v>128.16001</v>
       </c>
       <c r="H83">
-        <v>519.41558</v>
+        <v>519.4155786</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -5690,7 +5690,7 @@
         <v>126.9218</v>
       </c>
       <c r="H84">
-        <v>525.39697</v>
+        <v>451.8340534</v>
       </c>
     </row>
     <row r="85" spans="1:8">
@@ -5716,7 +5716,7 @@
         <v>229.25178</v>
       </c>
       <c r="H85">
-        <v>354.16777</v>
+        <v>354.1677691</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -5742,7 +5742,7 @@
         <v>182.44444</v>
       </c>
       <c r="H86">
-        <v>664.30092</v>
+        <v>664.3009152</v>
       </c>
     </row>
     <row r="87" spans="1:8">
@@ -5768,7 +5768,7 @@
         <v>173.68237</v>
       </c>
       <c r="H87">
-        <v>619.3963199999999</v>
+        <v>619.3963163</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -5794,7 +5794,7 @@
         <v>260.65776</v>
       </c>
       <c r="H88">
-        <v>450.63836</v>
+        <v>450.638355</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -5820,7 +5820,7 @@
         <v>236.51159</v>
       </c>
       <c r="H89">
-        <v>579.87161</v>
+        <v>579.8716123</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -5846,7 +5846,7 @@
         <v>233.30826</v>
       </c>
       <c r="H90">
-        <v>577.1749</v>
+        <v>577.1748971</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -5872,7 +5872,7 @@
         <v>23.98884</v>
       </c>
       <c r="H91">
-        <v>395.29699</v>
+        <v>395.2969935</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -5898,7 +5898,7 @@
         <v>41.81802</v>
       </c>
       <c r="H92">
-        <v>332.80078</v>
+        <v>332.8007788</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -5924,7 +5924,7 @@
         <v>259.31783</v>
       </c>
       <c r="H93">
-        <v>418.09939</v>
+        <v>418.099394</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -5950,7 +5950,7 @@
         <v>52.40945</v>
       </c>
       <c r="H94">
-        <v>707.74958</v>
+        <v>707.7495751</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -5976,7 +5976,7 @@
         <v>231.48782</v>
       </c>
       <c r="H95">
-        <v>693.82349</v>
+        <v>693.8234943</v>
       </c>
     </row>
     <row r="96" spans="1:8">
@@ -6002,7 +6002,7 @@
         <v>72.32787</v>
       </c>
       <c r="H96">
-        <v>298.25955</v>
+        <v>338.9486294</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6028,7 +6028,7 @@
         <v>126.61412</v>
       </c>
       <c r="H97">
-        <v>467.55388</v>
+        <v>467.5538802</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -6054,7 +6054,7 @@
         <v>88.44154</v>
       </c>
       <c r="H98">
-        <v>280.45227</v>
+        <v>280.4522691</v>
       </c>
     </row>
     <row r="99" spans="1:8">
@@ -6080,7 +6080,7 @@
         <v>241.62123</v>
       </c>
       <c r="H99">
-        <v>917.13836</v>
+        <v>832.720043</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -6106,7 +6106,7 @@
         <v>89.53051000000001</v>
       </c>
       <c r="H100">
-        <v>401.96956</v>
+        <v>401.9695612</v>
       </c>
     </row>
     <row r="101" spans="1:8">
@@ -6132,7 +6132,7 @@
         <v>131.42822</v>
       </c>
       <c r="H101">
-        <v>464.41372</v>
+        <v>400.915071</v>
       </c>
     </row>
     <row r="102" spans="1:8">
@@ -6158,7 +6158,7 @@
         <v>115.94355</v>
       </c>
       <c r="H102">
-        <v>300.49427</v>
+        <v>300.494269</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -6184,7 +6184,7 @@
         <v>107.65886</v>
       </c>
       <c r="H103">
-        <v>336.15146</v>
+        <v>336.151464</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -6210,7 +6210,7 @@
         <v>142.10406</v>
       </c>
       <c r="H104">
-        <v>466.79335</v>
+        <v>553.3749495</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6236,7 +6236,7 @@
         <v>47.59412</v>
       </c>
       <c r="H105">
-        <v>186.99033</v>
+        <v>186.9903296</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -6262,7 +6262,7 @@
         <v>35.53924</v>
       </c>
       <c r="H106">
-        <v>155.32239</v>
+        <v>155.3223911</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6288,7 +6288,7 @@
         <v>118.17872</v>
       </c>
       <c r="H107">
-        <v>322.77741</v>
+        <v>322.7774084</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6314,7 +6314,7 @@
         <v>39.14887</v>
       </c>
       <c r="H108">
-        <v>165.55987</v>
+        <v>165.5598681</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -6340,7 +6340,7 @@
         <v>73.14112</v>
       </c>
       <c r="H109">
-        <v>209.18602</v>
+        <v>209.1860175</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -6366,7 +6366,7 @@
         <v>87.09263</v>
       </c>
       <c r="H110">
-        <v>416.18112</v>
+        <v>416.1811155</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -6392,7 +6392,7 @@
         <v>141.30432</v>
       </c>
       <c r="H111">
-        <v>489.65872</v>
+        <v>489.6587206</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6418,7 +6418,7 @@
         <v>86.12266</v>
       </c>
       <c r="H112">
-        <v>273.45147</v>
+        <v>273.4514689</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -6444,7 +6444,7 @@
         <v>72.59419</v>
       </c>
       <c r="H113">
-        <v>370.48418</v>
+        <v>370.484185</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -6470,7 +6470,7 @@
         <v>132.21001</v>
       </c>
       <c r="H114">
-        <v>497.07981</v>
+        <v>497.0798123</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6496,7 +6496,7 @@
         <v>302.27121</v>
       </c>
       <c r="H115">
-        <v>709.22669</v>
+        <v>709.2266922</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -6522,7 +6522,7 @@
         <v>227.75303</v>
       </c>
       <c r="H116">
-        <v>477.68369</v>
+        <v>477.6836929</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6548,7 +6548,7 @@
         <v>169.26589</v>
       </c>
       <c r="H117">
-        <v>852.04914</v>
+        <v>852.0491449</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6574,7 +6574,7 @@
         <v>159.55675</v>
       </c>
       <c r="H118">
-        <v>819.92489</v>
+        <v>819.9248897</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -6600,7 +6600,7 @@
         <v>143.00192</v>
       </c>
       <c r="H119">
-        <v>561.3283699999999</v>
+        <v>561.3283703</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -6626,7 +6626,7 @@
         <v>158.67816</v>
       </c>
       <c r="H120">
-        <v>730.21847</v>
+        <v>749.8153241</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -6652,7 +6652,7 @@
         <v>153.94229</v>
       </c>
       <c r="H121">
-        <v>586.9592</v>
+        <v>586.9591986</v>
       </c>
     </row>
     <row r="122" spans="1:8">
@@ -6678,7 +6678,7 @@
         <v>161.90308</v>
       </c>
       <c r="H122">
-        <v>612.89495</v>
+        <v>612.8949503</v>
       </c>
     </row>
     <row r="123" spans="1:8">
@@ -6704,7 +6704,7 @@
         <v>92.36752</v>
       </c>
       <c r="H123">
-        <v>422.23107</v>
+        <v>464.3153328</v>
       </c>
     </row>
     <row r="124" spans="1:8">
@@ -6730,7 +6730,7 @@
         <v>118.35252</v>
       </c>
       <c r="H124">
-        <v>484.21995</v>
+        <v>484.2199473</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -6756,7 +6756,7 @@
         <v>113.1062</v>
       </c>
       <c r="H125">
-        <v>463.85631</v>
+        <v>463.8563116</v>
       </c>
     </row>
     <row r="126" spans="1:8">
@@ -6782,7 +6782,7 @@
         <v>101.59534</v>
       </c>
       <c r="H126">
-        <v>520.13043</v>
+        <v>520.1304272</v>
       </c>
     </row>
     <row r="127" spans="1:8">
@@ -6808,7 +6808,7 @@
         <v>220.01145</v>
       </c>
       <c r="H127">
-        <v>419.40455</v>
+        <v>419.4045524</v>
       </c>
     </row>
     <row r="128" spans="1:8">
@@ -6834,7 +6834,7 @@
         <v>62.33867</v>
       </c>
       <c r="H128">
-        <v>248.32719</v>
+        <v>248.3271857</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -6860,7 +6860,7 @@
         <v>219.0441</v>
       </c>
       <c r="H129">
-        <v>423.91348</v>
+        <v>423.9134757</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -6886,7 +6886,7 @@
         <v>99.56967</v>
       </c>
       <c r="H130">
-        <v>241.07684</v>
+        <v>241.0768415</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -6912,7 +6912,7 @@
         <v>90.65214</v>
       </c>
       <c r="H131">
-        <v>343.00658</v>
+        <v>410.7879131</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -6938,7 +6938,7 @@
         <v>87.79913999999999</v>
       </c>
       <c r="H132">
-        <v>382.95702</v>
+        <v>382.9570194</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -6964,7 +6964,7 @@
         <v>109.58448</v>
       </c>
       <c r="H133">
-        <v>231.01868</v>
+        <v>231.0186792</v>
       </c>
     </row>
     <row r="134" spans="1:8">
@@ -6990,7 +6990,7 @@
         <v>121.79808</v>
       </c>
       <c r="H134">
-        <v>256.94886</v>
+        <v>256.9488618</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -7016,7 +7016,7 @@
         <v>130.31399</v>
       </c>
       <c r="H135">
-        <v>269.56988</v>
+        <v>269.5698802</v>
       </c>
     </row>
     <row r="136" spans="1:8">
@@ -7042,7 +7042,7 @@
         <v>153.77229</v>
       </c>
       <c r="H136">
-        <v>515.53542</v>
+        <v>515.5354234</v>
       </c>
     </row>
     <row r="137" spans="1:8">
@@ -7068,7 +7068,7 @@
         <v>95.29161000000001</v>
       </c>
       <c r="H137">
-        <v>330.0786</v>
+        <v>330.0785981</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -7094,7 +7094,7 @@
         <v>157.81887</v>
       </c>
       <c r="H138">
-        <v>725.70934</v>
+        <v>696.5370036</v>
       </c>
     </row>
     <row r="139" spans="1:8">
@@ -7120,7 +7120,7 @@
         <v>18.89499</v>
       </c>
       <c r="H139">
-        <v>177.57976</v>
+        <v>177.5797629</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -7146,7 +7146,7 @@
         <v>29.59992</v>
       </c>
       <c r="H140">
-        <v>314.54145</v>
+        <v>314.5414469</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -7172,7 +7172,7 @@
         <v>24.32445</v>
       </c>
       <c r="H141">
-        <v>231.36075</v>
+        <v>231.3607452</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -7198,7 +7198,7 @@
         <v>169.2428</v>
       </c>
       <c r="H142">
-        <v>621.48786</v>
+        <v>711.6688193</v>
       </c>
     </row>
     <row r="143" spans="1:8">
@@ -7224,7 +7224,7 @@
         <v>72.96496</v>
       </c>
       <c r="H143">
-        <v>473.73322</v>
+        <v>473.7332174</v>
       </c>
     </row>
     <row r="144" spans="1:8">
@@ -7250,7 +7250,7 @@
         <v>161.18073</v>
       </c>
       <c r="H144">
-        <v>891.03539</v>
+        <v>891.0353914999999</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -7276,7 +7276,7 @@
         <v>223.65496</v>
       </c>
       <c r="H145">
-        <v>440.69985</v>
+        <v>446.3016398</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -7302,7 +7302,7 @@
         <v>208.75736</v>
       </c>
       <c r="H146">
-        <v>518.91803</v>
+        <v>452.5827389</v>
       </c>
     </row>
     <row r="147" spans="1:8">
@@ -7328,7 +7328,7 @@
         <v>229.98916</v>
       </c>
       <c r="H147">
-        <v>598.477</v>
+        <v>561.4369941</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -7354,7 +7354,7 @@
         <v>21.5545</v>
       </c>
       <c r="H148">
-        <v>193.49835</v>
+        <v>193.4983495</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -7380,7 +7380,7 @@
         <v>148.97688</v>
       </c>
       <c r="H149">
-        <v>346.89014</v>
+        <v>346.8901427</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -7406,7 +7406,7 @@
         <v>363.93848</v>
       </c>
       <c r="H150">
-        <v>732.38867</v>
+        <v>732.3886675</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -7432,7 +7432,7 @@
         <v>196.3084</v>
       </c>
       <c r="H151">
-        <v>552.99055</v>
+        <v>552.9905481</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -7458,7 +7458,7 @@
         <v>178.60763</v>
       </c>
       <c r="H152">
-        <v>700.38552</v>
+        <v>700.3855213000001</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -7484,7 +7484,7 @@
         <v>209.56416</v>
       </c>
       <c r="H153">
-        <v>380.24779</v>
+        <v>364.3485939</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -7510,7 +7510,7 @@
         <v>163.92498</v>
       </c>
       <c r="H154">
-        <v>521.98704</v>
+        <v>521.9870367</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -7536,7 +7536,7 @@
         <v>205.67612</v>
       </c>
       <c r="H155">
-        <v>615.9118099999999</v>
+        <v>615.9118124</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -7562,7 +7562,7 @@
         <v>264.35351</v>
       </c>
       <c r="H156">
-        <v>774.1966200000001</v>
+        <v>774.1966157000001</v>
       </c>
     </row>
     <row r="157" spans="1:8">
@@ -7588,7 +7588,7 @@
         <v>384.05046</v>
       </c>
       <c r="H157">
-        <v>1227.81227</v>
+        <v>1227.812274</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -7614,7 +7614,7 @@
         <v>44.32123</v>
       </c>
       <c r="H158">
-        <v>298.39138</v>
+        <v>298.3913792</v>
       </c>
     </row>
     <row r="159" spans="1:8">
@@ -7640,7 +7640,7 @@
         <v>170.21819</v>
       </c>
       <c r="H159">
-        <v>587.19998</v>
+        <v>587.1999836</v>
       </c>
     </row>
     <row r="160" spans="1:8">
@@ -7666,7 +7666,7 @@
         <v>217.56221</v>
       </c>
       <c r="H160">
-        <v>366.98849</v>
+        <v>366.9884885</v>
       </c>
     </row>
     <row r="161" spans="1:8">
@@ -7692,7 +7692,7 @@
         <v>199.6525</v>
       </c>
       <c r="H161">
-        <v>353.20662</v>
+        <v>353.2066236</v>
       </c>
     </row>
     <row r="162" spans="1:8">
@@ -7718,7 +7718,7 @@
         <v>178.09935</v>
       </c>
       <c r="H162">
-        <v>321.75491</v>
+        <v>321.7549101</v>
       </c>
     </row>
     <row r="163" spans="1:8">
@@ -7744,7 +7744,7 @@
         <v>40.6484</v>
       </c>
       <c r="H163">
-        <v>309.56607</v>
+        <v>400.208531</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -7770,7 +7770,7 @@
         <v>89.13056</v>
       </c>
       <c r="H164">
-        <v>441.92556</v>
+        <v>360.594013</v>
       </c>
     </row>
     <row r="165" spans="1:8">
@@ -7796,7 +7796,7 @@
         <v>294.55389</v>
       </c>
       <c r="H165">
-        <v>551.50046</v>
+        <v>458.4924911</v>
       </c>
     </row>
     <row r="166" spans="1:8">
@@ -7822,7 +7822,7 @@
         <v>276.00391</v>
       </c>
       <c r="H166">
-        <v>666.49973</v>
+        <v>666.4997254</v>
       </c>
     </row>
     <row r="167" spans="1:8">
@@ -7848,7 +7848,7 @@
         <v>43.81407</v>
       </c>
       <c r="H167">
-        <v>194.61495</v>
+        <v>199.7212421</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -7874,7 +7874,7 @@
         <v>28.59024</v>
       </c>
       <c r="H168">
-        <v>140.75528</v>
+        <v>140.7552773</v>
       </c>
     </row>
     <row r="169" spans="1:8">
@@ -7900,7 +7900,7 @@
         <v>30.04664</v>
       </c>
       <c r="H169">
-        <v>162.48932</v>
+        <v>162.4893194</v>
       </c>
     </row>
     <row r="170" spans="1:8">
@@ -7926,7 +7926,7 @@
         <v>68.87106</v>
       </c>
       <c r="H170">
-        <v>580.31916</v>
+        <v>580.3191593</v>
       </c>
     </row>
     <row r="171" spans="1:8">
@@ -7952,7 +7952,7 @@
         <v>219.01757</v>
       </c>
       <c r="H171">
-        <v>480.62429</v>
+        <v>480.6242885</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -7978,7 +7978,7 @@
         <v>131.0416</v>
       </c>
       <c r="H172">
-        <v>280.07696</v>
+        <v>280.0769591</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -8004,7 +8004,7 @@
         <v>63.71333</v>
       </c>
       <c r="H173">
-        <v>269.19458</v>
+        <v>217.7383202</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -8030,7 +8030,7 @@
         <v>66.00726</v>
       </c>
       <c r="H174">
-        <v>317.8159</v>
+        <v>317.8158959</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -8056,7 +8056,7 @@
         <v>25.65356</v>
       </c>
       <c r="H175">
-        <v>178.64575</v>
+        <v>205.3412638</v>
       </c>
     </row>
     <row r="176" spans="1:8">
@@ -8082,7 +8082,7 @@
         <v>68.28312</v>
       </c>
       <c r="H176">
-        <v>302.09962</v>
+        <v>250.6234581</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -8108,7 +8108,7 @@
         <v>145.79387</v>
       </c>
       <c r="H177">
-        <v>390.10668</v>
+        <v>302.4803302</v>
       </c>
     </row>
     <row r="178" spans="1:8">
@@ -8134,7 +8134,7 @@
         <v>32.17307</v>
       </c>
       <c r="H178">
-        <v>217.8814</v>
+        <v>217.8814034</v>
       </c>
     </row>
     <row r="179" spans="1:8">
@@ -8160,7 +8160,7 @@
         <v>57.85794</v>
       </c>
       <c r="H179">
-        <v>486.90299</v>
+        <v>486.9029931</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -8186,7 +8186,7 @@
         <v>32.2374</v>
       </c>
       <c r="H180">
-        <v>338.10001</v>
+        <v>338.1000125</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -8212,7 +8212,7 @@
         <v>77.20726000000001</v>
       </c>
       <c r="H181">
-        <v>215.21922</v>
+        <v>251.7498256</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -8238,7 +8238,7 @@
         <v>114.90021</v>
       </c>
       <c r="H182">
-        <v>497.03048</v>
+        <v>497.0304847</v>
       </c>
     </row>
     <row r="183" spans="1:8">
@@ -8264,7 +8264,7 @@
         <v>128.61488</v>
       </c>
       <c r="H183">
-        <v>511.87451</v>
+        <v>511.8745096</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -8290,7 +8290,7 @@
         <v>60.25476</v>
       </c>
       <c r="H184">
-        <v>329.45662</v>
+        <v>329.4566249</v>
       </c>
     </row>
     <row r="185" spans="1:8">
@@ -8316,7 +8316,7 @@
         <v>47.88654</v>
       </c>
       <c r="H185">
-        <v>222.62054</v>
+        <v>222.6205356</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -8342,7 +8342,7 @@
         <v>50.84094</v>
       </c>
       <c r="H186">
-        <v>225.09116</v>
+        <v>225.0911644</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -8368,7 +8368,7 @@
         <v>50.38625</v>
       </c>
       <c r="H187">
-        <v>229.00398</v>
+        <v>229.0039792</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -8394,7 +8394,7 @@
         <v>66.27348000000001</v>
       </c>
       <c r="H188">
-        <v>232.10747</v>
+        <v>232.107474</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -8420,7 +8420,7 @@
         <v>61.63564</v>
       </c>
       <c r="H189">
-        <v>241.37417</v>
+        <v>241.3741705</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -8446,7 +8446,7 @@
         <v>74.35039999999999</v>
       </c>
       <c r="H190">
-        <v>323.47263</v>
+        <v>323.4726262</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -8472,7 +8472,7 @@
         <v>94.36967</v>
       </c>
       <c r="H191">
-        <v>354.76848</v>
+        <v>334.299926</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -8498,7 +8498,7 @@
         <v>97.94146000000001</v>
       </c>
       <c r="H192">
-        <v>313.07582</v>
+        <v>313.0758176</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -8524,7 +8524,7 @@
         <v>79.16208</v>
       </c>
       <c r="H193">
-        <v>330.66379</v>
+        <v>330.6637947</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -8550,7 +8550,7 @@
         <v>74.03825999999999</v>
       </c>
       <c r="H194">
-        <v>272.96929</v>
+        <v>272.9692945</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -8576,7 +8576,7 @@
         <v>87.50960000000001</v>
       </c>
       <c r="H195">
-        <v>327.46937</v>
+        <v>327.4693713</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -8602,7 +8602,7 @@
         <v>312.76238</v>
       </c>
       <c r="H196">
-        <v>942.76393</v>
+        <v>942.7639263</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -8628,7 +8628,7 @@
         <v>52.63665</v>
       </c>
       <c r="H197">
-        <v>177.25314</v>
+        <v>177.2531398</v>
       </c>
     </row>
     <row r="198" spans="1:8">
@@ -8654,7 +8654,7 @@
         <v>141.11156</v>
       </c>
       <c r="H198">
-        <v>375.75354</v>
+        <v>350.4630564</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -8680,7 +8680,7 @@
         <v>492.65138</v>
       </c>
       <c r="H199">
-        <v>715.0512</v>
+        <v>715.0512043</v>
       </c>
     </row>
     <row r="200" spans="1:8">
@@ -8706,7 +8706,7 @@
         <v>94.95492</v>
       </c>
       <c r="H200">
-        <v>358.39892</v>
+        <v>358.3989233</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -8732,7 +8732,7 @@
         <v>84.47283</v>
       </c>
       <c r="H201">
-        <v>397.18852</v>
+        <v>397.1885199</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -8758,7 +8758,7 @@
         <v>303.31888</v>
       </c>
       <c r="H202">
-        <v>928.0195200000001</v>
+        <v>928.0195182</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -8784,7 +8784,7 @@
         <v>261.50837</v>
       </c>
       <c r="H203">
-        <v>611.65709</v>
+        <v>611.6570899</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -8810,7 +8810,7 @@
         <v>513.694</v>
       </c>
       <c r="H204">
-        <v>756.58901</v>
+        <v>756.5890108</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -8836,7 +8836,7 @@
         <v>540.0057</v>
       </c>
       <c r="H205">
-        <v>477.7506</v>
+        <v>477.7505967</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -8862,7 +8862,7 @@
         <v>458.01529</v>
       </c>
       <c r="H206">
-        <v>597.2382</v>
+        <v>597.2382041</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -8888,7 +8888,7 @@
         <v>610.5948100000001</v>
       </c>
       <c r="H207">
-        <v>1024.35784</v>
+        <v>1034.464762</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -8914,7 +8914,7 @@
         <v>117.05589</v>
       </c>
       <c r="H208">
-        <v>552.43666</v>
+        <v>552.4366552</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -8940,7 +8940,7 @@
         <v>454.40546</v>
       </c>
       <c r="H209">
-        <v>526.26586</v>
+        <v>526.2658596</v>
       </c>
     </row>
     <row r="210" spans="1:8">
@@ -8966,7 +8966,7 @@
         <v>82.94208</v>
       </c>
       <c r="H210">
-        <v>752.59376</v>
+        <v>752.5937591000001</v>
       </c>
     </row>
     <row r="211" spans="1:8">
@@ -9018,7 +9018,7 @@
         <v>76.23491</v>
       </c>
       <c r="H212">
-        <v>398.62786</v>
+        <v>398.6278645</v>
       </c>
     </row>
     <row r="213" spans="1:8">
@@ -9044,7 +9044,7 @@
         <v>99.99475</v>
       </c>
       <c r="H213">
-        <v>468.00983</v>
+        <v>468.0098261</v>
       </c>
     </row>
     <row r="214" spans="1:8">
@@ -9070,7 +9070,7 @@
         <v>14.08849</v>
       </c>
       <c r="H214">
-        <v>109.81432</v>
+        <v>202.5142899</v>
       </c>
     </row>
     <row r="215" spans="1:8">
@@ -9096,7 +9096,7 @@
         <v>487.72375</v>
       </c>
       <c r="H215">
-        <v>635.0802</v>
+        <v>635.0802036</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -9122,7 +9122,7 @@
         <v>78.41383</v>
       </c>
       <c r="H216">
-        <v>327.00642</v>
+        <v>293.7041079</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -9148,7 +9148,7 @@
         <v>110.15563</v>
       </c>
       <c r="H217">
-        <v>311.54665</v>
+        <v>288.93387</v>
       </c>
     </row>
     <row r="218" spans="1:8">
@@ -9174,7 +9174,7 @@
         <v>26.9531</v>
       </c>
       <c r="H218">
-        <v>133.09037</v>
+        <v>133.0903749</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -9200,7 +9200,7 @@
         <v>21.04633</v>
       </c>
       <c r="H219">
-        <v>124.44916</v>
+        <v>124.4491609</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -9226,7 +9226,7 @@
         <v>440.28539</v>
       </c>
       <c r="H220">
-        <v>830.68691</v>
+        <v>768.0301777</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -9252,7 +9252,7 @@
         <v>284.52929</v>
       </c>
       <c r="H221">
-        <v>731.51383</v>
+        <v>731.5138252</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -9278,7 +9278,7 @@
         <v>270.16179</v>
       </c>
       <c r="H222">
-        <v>618.12343</v>
+        <v>618.1234285</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -9304,7 +9304,7 @@
         <v>180.51808</v>
       </c>
       <c r="H223">
-        <v>482.76205</v>
+        <v>445.8698148</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -9330,7 +9330,7 @@
         <v>26.20582</v>
       </c>
       <c r="H224">
-        <v>238.26397</v>
+        <v>238.2639659</v>
       </c>
     </row>
     <row r="225" spans="1:8">
@@ -9356,7 +9356,7 @@
         <v>14.05075</v>
       </c>
       <c r="H225">
-        <v>252.99858</v>
+        <v>252.9985786</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -9408,7 +9408,7 @@
         <v>154.2002</v>
       </c>
       <c r="H227">
-        <v>616.65443</v>
+        <v>616.6544273</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -9434,7 +9434,7 @@
         <v>166.93757</v>
       </c>
       <c r="H228">
-        <v>866.29497</v>
+        <v>866.2949669</v>
       </c>
     </row>
     <row r="229" spans="1:8">
@@ -9460,7 +9460,7 @@
         <v>27.152</v>
       </c>
       <c r="H229">
-        <v>211.01839</v>
+        <v>211.0183942</v>
       </c>
     </row>
     <row r="230" spans="1:8">
@@ -9486,7 +9486,7 @@
         <v>36.12578</v>
       </c>
       <c r="H230">
-        <v>306.18744</v>
+        <v>306.1874354</v>
       </c>
     </row>
     <row r="231" spans="1:8">
@@ -9512,7 +9512,7 @@
         <v>86.80500000000001</v>
       </c>
       <c r="H231">
-        <v>448.47153</v>
+        <v>395.8292668</v>
       </c>
     </row>
     <row r="232" spans="1:8">
@@ -9538,7 +9538,7 @@
         <v>432.44695</v>
       </c>
       <c r="H232">
-        <v>1435.42304</v>
+        <v>1435.423041</v>
       </c>
     </row>
     <row r="233" spans="1:8">
@@ -9564,7 +9564,7 @@
         <v>226.55695</v>
       </c>
       <c r="H233">
-        <v>1027.51605</v>
+        <v>1027.516047</v>
       </c>
     </row>
     <row r="234" spans="1:8">
@@ -9590,7 +9590,7 @@
         <v>202.16712</v>
       </c>
       <c r="H234">
-        <v>775.31528</v>
+        <v>775.3152752</v>
       </c>
     </row>
     <row r="235" spans="1:8">
@@ -9616,7 +9616,7 @@
         <v>142.22267</v>
       </c>
       <c r="H235">
-        <v>557.39437</v>
+        <v>506.3153781</v>
       </c>
     </row>
     <row r="236" spans="1:8">
@@ -9642,7 +9642,7 @@
         <v>149.23344</v>
       </c>
       <c r="H236">
-        <v>747.20123</v>
+        <v>747.2012257</v>
       </c>
     </row>
     <row r="237" spans="1:8">
@@ -9668,7 +9668,7 @@
         <v>113.30953</v>
       </c>
       <c r="H237">
-        <v>543.9717000000001</v>
+        <v>543.9717043000001</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -9694,7 +9694,7 @@
         <v>189.00766</v>
       </c>
       <c r="H238">
-        <v>765.03389</v>
+        <v>685.3384036</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -9720,7 +9720,7 @@
         <v>147.21093</v>
       </c>
       <c r="H239">
-        <v>437.07447</v>
+        <v>437.0744671</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -9746,7 +9746,7 @@
         <v>363.57397</v>
       </c>
       <c r="H240">
-        <v>557.48843</v>
+        <v>557.4884296</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -9772,7 +9772,7 @@
         <v>216.85542</v>
       </c>
       <c r="H241">
-        <v>570.76475</v>
+        <v>570.7647456</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -9798,7 +9798,7 @@
         <v>194.46762</v>
       </c>
       <c r="H242">
-        <v>882.35128</v>
+        <v>882.3512757</v>
       </c>
     </row>
     <row r="243" spans="1:8">
@@ -9824,7 +9824,7 @@
         <v>201.28452</v>
       </c>
       <c r="H243">
-        <v>638.78368</v>
+        <v>638.7836822</v>
       </c>
     </row>
     <row r="244" spans="1:8">
@@ -9850,7 +9850,7 @@
         <v>147.55167</v>
       </c>
       <c r="H244">
-        <v>684.05995</v>
+        <v>684.0599486</v>
       </c>
     </row>
     <row r="245" spans="1:8">
@@ -9876,7 +9876,7 @@
         <v>90.84253</v>
       </c>
       <c r="H245">
-        <v>406.27367</v>
+        <v>406.273668</v>
       </c>
     </row>
     <row r="246" spans="1:8">
@@ -9902,7 +9902,7 @@
         <v>124.69511</v>
       </c>
       <c r="H246">
-        <v>536.61671</v>
+        <v>536.6167127</v>
       </c>
     </row>
     <row r="247" spans="1:8">
@@ -9928,7 +9928,7 @@
         <v>114.77002</v>
       </c>
       <c r="H247">
-        <v>420.42559</v>
+        <v>420.4255852</v>
       </c>
     </row>
     <row r="248" spans="1:8">
@@ -9954,7 +9954,7 @@
         <v>185.09152</v>
       </c>
       <c r="H248">
-        <v>417.42852</v>
+        <v>417.4285182</v>
       </c>
     </row>
     <row r="249" spans="1:8">
@@ -9980,7 +9980,7 @@
         <v>255.73322</v>
       </c>
       <c r="H249">
-        <v>443.81403</v>
+        <v>443.8140327</v>
       </c>
     </row>
     <row r="250" spans="1:8">
@@ -10006,7 +10006,7 @@
         <v>213.94478</v>
       </c>
       <c r="H250">
-        <v>465.22274</v>
+        <v>465.2227385</v>
       </c>
     </row>
     <row r="251" spans="1:8">
@@ -10032,7 +10032,7 @@
         <v>107.10102</v>
       </c>
       <c r="H251">
-        <v>304.53646</v>
+        <v>304.5364597</v>
       </c>
     </row>
     <row r="252" spans="1:8">
@@ -10058,7 +10058,7 @@
         <v>103.31971</v>
       </c>
       <c r="H252">
-        <v>274.73921</v>
+        <v>274.7392086</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -10084,7 +10084,7 @@
         <v>180.9457</v>
       </c>
       <c r="H253">
-        <v>343.10512</v>
+        <v>343.1051242</v>
       </c>
     </row>
     <row r="254" spans="1:8">
@@ -10110,7 +10110,7 @@
         <v>173.01438</v>
       </c>
       <c r="H254">
-        <v>313.78238</v>
+        <v>313.7823794</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -10136,7 +10136,7 @@
         <v>195.05572</v>
       </c>
       <c r="H255">
-        <v>756.97577</v>
+        <v>756.9757738</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -10162,7 +10162,7 @@
         <v>333.42278</v>
       </c>
       <c r="H256">
-        <v>623.47487</v>
+        <v>623.474866</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -10188,7 +10188,7 @@
         <v>198.61598</v>
       </c>
       <c r="H257">
-        <v>394.58845</v>
+        <v>394.5884459</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -10214,7 +10214,7 @@
         <v>127.02152</v>
       </c>
       <c r="H258">
-        <v>298.79268</v>
+        <v>203.9250228</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -10240,7 +10240,7 @@
         <v>120.16904</v>
       </c>
       <c r="H259">
-        <v>294.4517</v>
+        <v>200.5174778</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -10266,7 +10266,7 @@
         <v>177.41646</v>
       </c>
       <c r="H260">
-        <v>491.30363</v>
+        <v>491.3036265</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -10292,7 +10292,7 @@
         <v>137.02661</v>
       </c>
       <c r="H261">
-        <v>303.48091</v>
+        <v>303.4809128</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -10318,7 +10318,7 @@
         <v>92.08426</v>
       </c>
       <c r="H262">
-        <v>328.2903</v>
+        <v>328.2903048</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -10344,7 +10344,7 @@
         <v>85.22784</v>
       </c>
       <c r="H263">
-        <v>272.84599</v>
+        <v>357.9791315</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -10370,7 +10370,7 @@
         <v>94.12739000000001</v>
       </c>
       <c r="H264">
-        <v>352.92671</v>
+        <v>352.9267116</v>
       </c>
     </row>
     <row r="265" spans="1:8">
@@ -10396,7 +10396,7 @@
         <v>89.57259999999999</v>
       </c>
       <c r="H265">
-        <v>307.21527</v>
+        <v>316.527704</v>
       </c>
     </row>
     <row r="266" spans="1:8">
@@ -10422,7 +10422,7 @@
         <v>174.35023</v>
       </c>
       <c r="H266">
-        <v>344.13052</v>
+        <v>344.1305187</v>
       </c>
     </row>
     <row r="267" spans="1:8">
@@ -10448,7 +10448,7 @@
         <v>89.0432</v>
       </c>
       <c r="H267">
-        <v>371.9587</v>
+        <v>285.9559114</v>
       </c>
     </row>
     <row r="268" spans="1:8">
@@ -10474,7 +10474,7 @@
         <v>195.03378</v>
       </c>
       <c r="H268">
-        <v>407.47747</v>
+        <v>407.4774732</v>
       </c>
     </row>
     <row r="269" spans="1:8">
@@ -10500,7 +10500,7 @@
         <v>295.88682</v>
       </c>
       <c r="H269">
-        <v>472.57357</v>
+        <v>472.5735682</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -10526,7 +10526,7 @@
         <v>315.56182</v>
       </c>
       <c r="H270">
-        <v>479.73639</v>
+        <v>479.7363897</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -10552,7 +10552,7 @@
         <v>138.32259</v>
       </c>
       <c r="H271">
-        <v>330.16704</v>
+        <v>330.167041</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -10578,7 +10578,7 @@
         <v>409.66693</v>
       </c>
       <c r="H272">
-        <v>504.55633</v>
+        <v>504.5563251</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -10604,7 +10604,7 @@
         <v>303.85353</v>
       </c>
       <c r="H273">
-        <v>474.18736</v>
+        <v>474.1873566</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -10630,7 +10630,7 @@
         <v>170.277</v>
       </c>
       <c r="H274">
-        <v>392.67285</v>
+        <v>392.6728517</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -10656,7 +10656,7 @@
         <v>344.29406</v>
       </c>
       <c r="H275">
-        <v>488.03804</v>
+        <v>488.038045</v>
       </c>
     </row>
     <row r="276" spans="1:8">
@@ -10682,7 +10682,7 @@
         <v>215.54708</v>
       </c>
       <c r="H276">
-        <v>330.69874</v>
+        <v>330.6987366</v>
       </c>
     </row>
     <row r="277" spans="1:8">
@@ -10708,7 +10708,7 @@
         <v>234.93056</v>
       </c>
       <c r="H277">
-        <v>346.69835</v>
+        <v>346.6983515</v>
       </c>
     </row>
     <row r="278" spans="1:8">
@@ -10734,7 +10734,7 @@
         <v>215.30166</v>
       </c>
       <c r="H278">
-        <v>439.47724</v>
+        <v>439.477241</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -10760,7 +10760,7 @@
         <v>182.06357</v>
       </c>
       <c r="H279">
-        <v>298.08859</v>
+        <v>298.0885885</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -10786,7 +10786,7 @@
         <v>371.12682</v>
       </c>
       <c r="H280">
-        <v>880.13698</v>
+        <v>880.136975</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -10812,7 +10812,7 @@
         <v>255.29498</v>
       </c>
       <c r="H281">
-        <v>461.20344</v>
+        <v>417.5958751</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -10838,7 +10838,7 @@
         <v>288.42497</v>
       </c>
       <c r="H282">
-        <v>473.47625</v>
+        <v>473.4762492</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -10864,7 +10864,7 @@
         <v>223.61314</v>
       </c>
       <c r="H283">
-        <v>348.11372</v>
+        <v>348.113725</v>
       </c>
     </row>
     <row r="284" spans="1:8">
@@ -10890,7 +10890,7 @@
         <v>70.40774</v>
       </c>
       <c r="H284">
-        <v>272.78751</v>
+        <v>272.7875117</v>
       </c>
     </row>
     <row r="285" spans="1:8">
@@ -10916,7 +10916,7 @@
         <v>69.83468999999999</v>
       </c>
       <c r="H285">
-        <v>267.2891</v>
+        <v>267.2890989</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -10942,7 +10942,7 @@
         <v>467.44788</v>
       </c>
       <c r="H286">
-        <v>927.57663</v>
+        <v>927.5766307</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -10968,7 +10968,7 @@
         <v>289.26941</v>
       </c>
       <c r="H287">
-        <v>612.75586</v>
+        <v>612.7558575</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -10994,7 +10994,7 @@
         <v>325.8513</v>
       </c>
       <c r="H288">
-        <v>484.27178</v>
+        <v>484.2717801</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -11020,7 +11020,7 @@
         <v>194.91228</v>
       </c>
       <c r="H289">
-        <v>307.23703</v>
+        <v>307.2370336</v>
       </c>
     </row>
     <row r="290" spans="1:8">
@@ -11046,7 +11046,7 @@
         <v>249.82868</v>
       </c>
       <c r="H290">
-        <v>404.01046</v>
+        <v>404.010464</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -11072,7 +11072,7 @@
         <v>369.26017</v>
       </c>
       <c r="H291">
-        <v>652.79842</v>
+        <v>652.7984212</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -11098,7 +11098,7 @@
         <v>114.05856</v>
       </c>
       <c r="H292">
-        <v>380.10632</v>
+        <v>380.1063223</v>
       </c>
     </row>
     <row r="293" spans="1:8">
@@ -11124,7 +11124,7 @@
         <v>132.86364</v>
       </c>
       <c r="H293">
-        <v>334.38993</v>
+        <v>334.3899309</v>
       </c>
     </row>
     <row r="294" spans="1:8">
@@ -11150,7 +11150,7 @@
         <v>209.7887</v>
       </c>
       <c r="H294">
-        <v>360.49747</v>
+        <v>290.5057968</v>
       </c>
     </row>
     <row r="295" spans="1:8">
@@ -11176,7 +11176,7 @@
         <v>65.69779</v>
       </c>
       <c r="H295">
-        <v>230.83635</v>
+        <v>182.128849</v>
       </c>
     </row>
     <row r="296" spans="1:8">
